--- a/Anumoy_Pathak_RedBus/Bus_Seat_Booking_Test_Cases.xlsx
+++ b/Anumoy_Pathak_RedBus/Bus_Seat_Booking_Test_Cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1d6a5426fd29e00d/Desktop/Anumoy_Pathak_RedBus/Anumoy_Pathak_RedBus/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="89" documentId="11_0621C7051479C63F611C0497582D1E7DC9FCB162" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16DE2789-0F60-49BB-9987-C5F1631CA806}"/>
+  <xr:revisionPtr revIDLastSave="95" documentId="11_0621C7051479C63F611C0497582D1E7DC9FCB162" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1686202A-252A-40EB-8E19-E369A953F02E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="173">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -651,7 +651,14 @@
     <t>Contact details are valid and in the payment page the QR is displayed successfully when UPI option is selected</t>
   </si>
   <si>
-    <t>Comments</t>
+    <t>Comment</t>
+  </si>
+  <si>
+    <t>Actual Result Iteration 2</t>
+  </si>
+  <si>
+    <t>Status
+ Iteration 2</t>
   </si>
   <si>
     <t>Req: Reference</t>
@@ -785,7 +792,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -802,7 +809,6 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -832,6 +838,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1155,10 +1167,10 @@
     <col min="6" max="6" width="30" customWidth="1"/>
     <col min="7" max="8" width="44" customWidth="1"/>
     <col min="9" max="9" width="16" customWidth="1"/>
-    <col min="10" max="10" width="28.77734375" customWidth="1"/>
-    <col min="11" max="11" width="17.33203125" customWidth="1"/>
-    <col min="12" max="12" width="16.5546875" customWidth="1"/>
-    <col min="13" max="13" width="18" customWidth="1"/>
+    <col min="10" max="10" width="26.44140625" customWidth="1"/>
+    <col min="11" max="11" width="14" customWidth="1"/>
+    <col min="12" max="12" width="14.21875" customWidth="1"/>
+    <col min="13" max="13" width="17.44140625" customWidth="1"/>
     <col min="14" max="14" width="8.88671875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1184,23 +1196,23 @@
       <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="K1" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="L1" s="6" t="s">
+      <c r="J1" s="17" t="s">
+        <v>169</v>
+      </c>
+      <c r="K1" s="17" t="s">
+        <v>170</v>
+      </c>
+      <c r="L1" s="17" t="s">
         <v>168</v>
       </c>
-      <c r="M1" s="6" t="s">
-        <v>169</v>
+      <c r="M1" s="17" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="115.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -1222,13 +1234,13 @@
       <c r="F2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="H2" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="I2" s="11" t="s">
+      <c r="I2" s="10" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1251,13 +1263,13 @@
       <c r="F3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="H3" s="12" t="s">
+      <c r="H3" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="I3" s="11" t="s">
+      <c r="I3" s="10" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1280,13 +1292,13 @@
       <c r="F4" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="H4" s="10" t="s">
+      <c r="H4" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="10" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1309,13 +1321,13 @@
       <c r="F5" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="G5" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="12" t="s">
+      <c r="H5" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="I5" s="11" t="s">
+      <c r="I5" s="10" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1338,13 +1350,13 @@
       <c r="F6" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="G6" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="H6" s="10" t="s">
+      <c r="H6" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="I6" s="11" t="s">
+      <c r="I6" s="10" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1370,10 +1382,10 @@
       <c r="G7" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="H7" s="12" t="s">
+      <c r="H7" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="I7" s="11" t="s">
+      <c r="I7" s="10" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1399,10 +1411,10 @@
       <c r="G8" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="H8" s="10" t="s">
+      <c r="H8" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="I8" s="11" t="s">
+      <c r="I8" s="10" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1428,10 +1440,10 @@
       <c r="G9" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="H9" s="12" t="s">
+      <c r="H9" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="I9" s="11" t="s">
+      <c r="I9" s="10" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1457,10 +1469,10 @@
       <c r="G10" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="H10" s="10" t="s">
+      <c r="H10" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="I10" s="11" t="s">
+      <c r="I10" s="10" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1486,10 +1498,10 @@
       <c r="G11" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="H11" s="12" t="s">
+      <c r="H11" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="I11" s="11" t="s">
+      <c r="I11" s="10" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1515,10 +1527,10 @@
       <c r="G12" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="H12" s="12" t="s">
+      <c r="H12" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="I12" s="11" t="s">
+      <c r="I12" s="10" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1544,10 +1556,10 @@
       <c r="G13" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="H13" s="10" t="s">
+      <c r="H13" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="I13" s="11" t="s">
+      <c r="I13" s="10" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1573,10 +1585,10 @@
       <c r="G14" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="H14" s="12" t="s">
+      <c r="H14" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="I14" s="11" t="s">
+      <c r="I14" s="10" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1602,10 +1614,10 @@
       <c r="G15" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="H15" s="12" t="s">
+      <c r="H15" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="I15" s="11" t="s">
+      <c r="I15" s="10" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1631,20 +1643,20 @@
       <c r="G16" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="H16" s="14" t="s">
+      <c r="H16" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="I16" s="13" t="s">
+      <c r="I16" s="12" t="s">
         <v>150</v>
       </c>
-      <c r="J16" s="16" t="s">
+      <c r="J16" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="K16" s="13" t="s">
+      <c r="K16" s="12" t="s">
         <v>150</v>
       </c>
-      <c r="L16" s="16" t="s">
-        <v>170</v>
+      <c r="L16" s="15" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="115.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -1669,10 +1681,10 @@
       <c r="G17" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="H17" s="14" t="s">
+      <c r="H17" s="13" t="s">
         <v>151</v>
       </c>
-      <c r="I17" s="11" t="s">
+      <c r="I17" s="10" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1698,10 +1710,10 @@
       <c r="G18" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="H18" s="12" t="s">
+      <c r="H18" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="I18" s="11" t="s">
+      <c r="I18" s="10" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1727,10 +1739,10 @@
       <c r="G19" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="H19" s="10" t="s">
+      <c r="H19" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="I19" s="11" t="s">
+      <c r="I19" s="10" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1756,10 +1768,10 @@
       <c r="G20" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="H20" s="15" t="s">
+      <c r="H20" s="14" t="s">
         <v>156</v>
       </c>
-      <c r="I20" s="11" t="s">
+      <c r="I20" s="10" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1785,10 +1797,10 @@
       <c r="G21" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="H21" s="10" t="s">
+      <c r="H21" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="I21" s="11" t="s">
+      <c r="I21" s="10" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1814,10 +1826,10 @@
       <c r="G22" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="H22" s="12" t="s">
+      <c r="H22" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="I22" s="11" t="s">
+      <c r="I22" s="10" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1843,10 +1855,10 @@
       <c r="G23" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="H23" s="10" t="s">
+      <c r="H23" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="I23" s="11" t="s">
+      <c r="I23" s="10" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1872,10 +1884,10 @@
       <c r="G24" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="H24" s="12" t="s">
+      <c r="H24" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="I24" s="11" t="s">
+      <c r="I24" s="10" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1901,10 +1913,10 @@
       <c r="G25" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="H25" s="15" t="s">
+      <c r="H25" s="14" t="s">
         <v>167</v>
       </c>
-      <c r="I25" s="11" t="s">
+      <c r="I25" s="10" t="s">
         <v>15</v>
       </c>
     </row>
